--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/10_Bankkonto_Umsatzliste.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/10_Bankkonto_Umsatzliste.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVoba_771102" sheetId="1" r:id="R9a1b6af4bbd94493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sparkasse_3390" sheetId="2" r:id="Ra3d5e3a918b84f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontenstatus" sheetId="3" r:id="R96d0db9e6f164a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVoba_771102" sheetId="1" r:id="R934dda92d6d041b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sparkasse_3390" sheetId="2" r:id="Rd30fc0953f754572"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontenstatus" sheetId="3" r:id="Rd91f440a1e9c4120"/>
   </x:sheets>
 </x:workbook>
 </file>
